--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41B4713A-335D-402E-80E0-8E74B3143F80}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18DFF84D-D316-49B4-BB15-C4005F5B7E1C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
     <sheet name="Matchups" sheetId="2" r:id="rId2"/>
+    <sheet name="Cup" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -107,6 +108,30 @@
   </si>
   <si>
     <t>Week</t>
+  </si>
+  <si>
+    <t>a_team_id</t>
+  </si>
+  <si>
+    <t>b_team_id</t>
+  </si>
+  <si>
+    <t>match_id</t>
+  </si>
+  <si>
+    <t>a_team_score</t>
+  </si>
+  <si>
+    <t>b_team_score</t>
+  </si>
+  <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>QF</t>
+  </si>
+  <si>
+    <t>Leg</t>
   </si>
 </sst>
 </file>
@@ -735,4 +760,134 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C26BBF9-15A1-4BF0-95EE-95BBAF4D7DE0}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>150</v>
+      </c>
+      <c r="E2">
+        <v>125</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>111</v>
+      </c>
+      <c r="E3">
+        <v>110</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>143</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>78</v>
+      </c>
+      <c r="E5">
+        <v>88</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18DFF84D-D316-49B4-BB15-C4005F5B7E1C}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D3353F8-049A-4F17-B7E5-79A70C804A76}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
     <sheet name="Matchups" sheetId="2" r:id="rId2"/>
     <sheet name="Cup" sheetId="3" r:id="rId3"/>
+    <sheet name="Waivers" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -95,18 +96,6 @@
     <t>Nick</t>
   </si>
   <si>
-    <t>win_team_id</t>
-  </si>
-  <si>
-    <t>loss_team_id</t>
-  </si>
-  <si>
-    <t>win_team_points</t>
-  </si>
-  <si>
-    <t>loss_team_points</t>
-  </si>
-  <si>
     <t>Week</t>
   </si>
   <si>
@@ -132,6 +121,132 @@
   </si>
   <si>
     <t>Leg</t>
+  </si>
+  <si>
+    <t>home_team_id</t>
+  </si>
+  <si>
+    <t>away_team_id</t>
+  </si>
+  <si>
+    <t>transaction_id</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>FAAB</t>
+  </si>
+  <si>
+    <t>team_id</t>
+  </si>
+  <si>
+    <t>Jaka Bijol</t>
+  </si>
+  <si>
+    <t>Mamadou Sangaré</t>
+  </si>
+  <si>
+    <t>Jack Hinshelwood</t>
+  </si>
+  <si>
+    <t>Ola Aina</t>
+  </si>
+  <si>
+    <t>Amar Dedic</t>
+  </si>
+  <si>
+    <t>Lukáš Horníček</t>
+  </si>
+  <si>
+    <t>Matias Fernandez-Pardo</t>
+  </si>
+  <si>
+    <t>Daizen Maeda</t>
+  </si>
+  <si>
+    <t>Ross Barkley</t>
+  </si>
+  <si>
+    <t>Bradley Barcola</t>
+  </si>
+  <si>
+    <t>Oliver McBurnie</t>
+  </si>
+  <si>
+    <t>Justin Kluivert</t>
+  </si>
+  <si>
+    <t>Tyrique George</t>
+  </si>
+  <si>
+    <t>Ayyoub Bouaddi</t>
+  </si>
+  <si>
+    <t>Konstantinos Tzolakis</t>
+  </si>
+  <si>
+    <t>Keane Lewis-Potter</t>
+  </si>
+  <si>
+    <t>Nobel Mendy</t>
+  </si>
+  <si>
+    <t>Vitaly Janelt</t>
+  </si>
+  <si>
+    <t>Emersonn</t>
+  </si>
+  <si>
+    <t>Mykhailo Mudryk</t>
+  </si>
+  <si>
+    <t>Semi Ajayi</t>
+  </si>
+  <si>
+    <t>Ibrahim Mbaye</t>
+  </si>
+  <si>
+    <t>Malick Fofana</t>
+  </si>
+  <si>
+    <t>James Justin</t>
+  </si>
+  <si>
+    <t>Julian Alvarez</t>
+  </si>
+  <si>
+    <t>Lee Davis</t>
+  </si>
+  <si>
+    <t>Mohamed Belloumi</t>
+  </si>
+  <si>
+    <t>Lewis Hall</t>
+  </si>
+  <si>
+    <t>Jarrad Branthwaite</t>
+  </si>
+  <si>
+    <t>Julio Enciso</t>
+  </si>
+  <si>
+    <t>Oscar Bobb</t>
+  </si>
+  <si>
+    <t>Leon Goretzka</t>
+  </si>
+  <si>
+    <t>Abdul Fatawu</t>
+  </si>
+  <si>
+    <t>Home_team_points</t>
+  </si>
+  <si>
+    <t>Away_team_points</t>
   </si>
 </sst>
 </file>
@@ -167,8 +282,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,30 +711,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBDA112-4455-493F-9D63-4B72BBDFDC28}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -640,16 +753,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
       <c r="C3">
+        <v>80.5</v>
+      </c>
+      <c r="D3">
         <v>107.5</v>
-      </c>
-      <c r="D3">
-        <v>80.5</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -691,16 +804,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
       <c r="C6">
+        <v>76.5</v>
+      </c>
+      <c r="D6">
         <v>97.25</v>
-      </c>
-      <c r="D6">
-        <v>76.5</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -755,6 +868,74 @@
       </c>
       <c r="E9">
         <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>62.25</v>
+      </c>
+      <c r="D10">
+        <v>103.75</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>96</v>
+      </c>
+      <c r="D11">
+        <v>102.75</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>96.25</v>
+      </c>
+      <c r="D12">
+        <v>93</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>97.75</v>
+      </c>
+      <c r="D13">
+        <v>92.5</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -774,25 +955,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -812,7 +993,7 @@
         <v>125</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -835,7 +1016,7 @@
         <v>110</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -858,7 +1039,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -881,7 +1062,7 @@
         <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -890,4 +1071,600 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE21E41-8143-4B31-AF43-B1572AB93726}">
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46267</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46261</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46267</v>
+      </c>
+      <c r="D23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46267</v>
+      </c>
+      <c r="D24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>6</v>
+      </c>
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>7</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D29" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>7</v>
+      </c>
+      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>8</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>8</v>
+      </c>
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46258</v>
+      </c>
+      <c r="D32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>8</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33" s="1">
+        <v>46262</v>
+      </c>
+      <c r="D33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>8</v>
+      </c>
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34" s="1">
+        <v>46265</v>
+      </c>
+      <c r="D34" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D3353F8-049A-4F17-B7E5-79A70C804A76}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F89265F-DFED-434B-8485-2DEC801194A8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
@@ -759,10 +759,10 @@
         <v>4</v>
       </c>
       <c r="C3">
+        <v>107.5</v>
+      </c>
+      <c r="D3">
         <v>80.5</v>
-      </c>
-      <c r="D3">
-        <v>107.5</v>
       </c>
       <c r="E3">
         <v>1</v>

--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F89265F-DFED-434B-8485-2DEC801194A8}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E74A74EC-40FA-4C52-95C8-39AB73D77E98}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="78">
   <si>
     <t>ID</t>
   </si>
@@ -247,6 +247,30 @@
   </si>
   <si>
     <t>Away_team_points</t>
+  </si>
+  <si>
+    <t>James Mcatee</t>
+  </si>
+  <si>
+    <t>Exequiel Palacios</t>
+  </si>
+  <si>
+    <t>Favorite_Team</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>West Ham</t>
+  </si>
+  <si>
+    <t>Spurs</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
   </si>
 </sst>
 </file>
@@ -599,13 +623,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE574477-F8B8-4C54-8D52-90DE47CC4CEE}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -615,8 +639,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -626,8 +653,11 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -637,8 +667,11 @@
       <c r="C3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -648,8 +681,11 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -659,8 +695,11 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -671,7 +710,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -681,8 +720,11 @@
       <c r="C7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -692,8 +734,11 @@
       <c r="C8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -702,6 +747,9 @@
       </c>
       <c r="C9" t="s">
         <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1075,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE21E41-8143-4B31-AF43-B1572AB93726}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
@@ -1663,6 +1711,57 @@
         <v>53</v>
       </c>
     </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46271</v>
+      </c>
+      <c r="D35" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36">
+        <v>35</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46271</v>
+      </c>
+      <c r="D36" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>5</v>
+      </c>
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46271</v>
+      </c>
+      <c r="D37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E74A74EC-40FA-4C52-95C8-39AB73D77E98}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2EEFFCC-AD09-4F7E-8D36-C82B4FEAA369}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
+    <workbookView xWindow="-14505" yWindow="1815" windowWidth="14610" windowHeight="15585" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Brighton</t>
   </si>
 </sst>
 </file>
@@ -709,6 +712,9 @@
       <c r="C6" t="s">
         <v>12</v>
       </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">

--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2EEFFCC-AD09-4F7E-8D36-C82B4FEAA369}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7741F91E-341F-4FF3-8CAC-36C7D54C7433}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="1815" windowWidth="14610" windowHeight="15585" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -274,6 +274,57 @@
   </si>
   <si>
     <t>Brighton</t>
+  </si>
+  <si>
+    <t>League_week</t>
+  </si>
+  <si>
+    <t>Week 19</t>
+  </si>
+  <si>
+    <t>Week 20</t>
+  </si>
+  <si>
+    <t>Week 22</t>
+  </si>
+  <si>
+    <t>Week 23</t>
+  </si>
+  <si>
+    <t>Week 25</t>
+  </si>
+  <si>
+    <t>Week 26</t>
+  </si>
+  <si>
+    <t>Week 28</t>
+  </si>
+  <si>
+    <t>Week 29</t>
+  </si>
+  <si>
+    <t>Week 31</t>
+  </si>
+  <si>
+    <t>Week 32</t>
+  </si>
+  <si>
+    <t>Week 34</t>
+  </si>
+  <si>
+    <t>Week 35</t>
+  </si>
+  <si>
+    <t>Week 37</t>
+  </si>
+  <si>
+    <t>Week 38</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>Final</t>
   </si>
 </sst>
 </file>
@@ -297,7 +348,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -305,13 +356,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,15 +1060,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C26BBF9-15A1-4BF0-95EE-95BBAF4D7DE0}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="1" max="8" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1029,22 +1088,13 @@
       <c r="G1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>150</v>
-      </c>
-      <c r="E2">
-        <v>125</v>
       </c>
       <c r="F2" t="s">
         <v>26</v>
@@ -1052,74 +1102,190 @@
       <c r="G2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>111</v>
-      </c>
-      <c r="E3">
-        <v>110</v>
-      </c>
       <c r="F3" t="s">
         <v>26</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>143</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
       <c r="F4" t="s">
         <v>26</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>78</v>
-      </c>
-      <c r="E5">
-        <v>88</v>
-      </c>
       <c r="F5" t="s">
         <v>26</v>
       </c>
       <c r="G5">
         <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7741F91E-341F-4FF3-8CAC-36C7D54C7433}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA3095A0-BF01-47DD-BE42-CD63F833A07C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
+    <workbookView xWindow="-20010" yWindow="2415" windowWidth="13500" windowHeight="10545" activeTab="1" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -325,6 +325,12 @@
   </si>
   <si>
     <t>Final</t>
+  </si>
+  <si>
+    <t>Home_team_best_lineup</t>
+  </si>
+  <si>
+    <t>Away_team_best_lineup</t>
   </si>
 </sst>
 </file>
@@ -369,10 +375,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -826,230 +841,309 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBDA112-4455-493F-9D63-4B72BBDFDC28}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="10.5703125" customWidth="1"/>
+    <col min="1" max="7" width="16.28515625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
         <v>3</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>99.5</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>71.5</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="E2" s="3">
+        <v>149.75</v>
+      </c>
+      <c r="F2" s="3">
+        <v>83.75</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>107.5</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>80.5</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="E3" s="3">
+        <v>115.25</v>
+      </c>
+      <c r="F3" s="3">
+        <v>88.25</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>7</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>79.75</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>76</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="E4" s="3">
+        <v>101</v>
+      </c>
+      <c r="F4" s="3">
+        <v>79.5</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>118.25</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>111.25</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
+      <c r="E5" s="3">
+        <v>132</v>
+      </c>
+      <c r="F5" s="3">
+        <v>129.75</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>76.5</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="3">
+        <v>75</v>
+      </c>
+      <c r="D6" s="3">
         <v>97.25</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
+        <v>94.75</v>
+      </c>
+      <c r="F6" s="3">
+        <v>127.75</v>
+      </c>
+      <c r="G6" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>106</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>98.25</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
+        <v>135.25</v>
+      </c>
+      <c r="F7" s="3">
+        <v>123.25</v>
+      </c>
+      <c r="G7" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>3</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>103.25</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>95</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
+        <v>145.25</v>
+      </c>
+      <c r="F8" s="3">
+        <v>100.5</v>
+      </c>
+      <c r="G8" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>5</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>157.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="3">
         <v>131.25</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3">
+        <v>171</v>
+      </c>
+      <c r="F9" s="3">
+        <v>135.5</v>
+      </c>
+      <c r="G9" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3">
         <v>5</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>62.25</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="3">
         <v>103.75</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3">
+        <v>75</v>
+      </c>
+      <c r="F10" s="3">
+        <v>120.75</v>
+      </c>
+      <c r="G10" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>4</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>7</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>96</v>
       </c>
-      <c r="D11">
-        <v>102.75</v>
-      </c>
-      <c r="E11">
+      <c r="D11" s="3">
+        <v>101.75</v>
+      </c>
+      <c r="E11" s="3">
+        <v>134</v>
+      </c>
+      <c r="F11" s="3">
+        <v>116.75</v>
+      </c>
+      <c r="G11" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>3</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>8</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>96.25</v>
       </c>
-      <c r="D12">
-        <v>93</v>
-      </c>
-      <c r="E12">
+      <c r="D12" s="3">
+        <v>92.5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>104.75</v>
+      </c>
+      <c r="F12" s="3">
+        <v>124.75</v>
+      </c>
+      <c r="G12" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>2</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>6</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>97.75</v>
       </c>
-      <c r="D13">
-        <v>92.5</v>
-      </c>
-      <c r="E13">
+      <c r="D13" s="3">
+        <v>91.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>132.25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>116.5</v>
+      </c>
+      <c r="G13" s="3">
         <v>3</v>
       </c>
     </row>

--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA3095A0-BF01-47DD-BE42-CD63F833A07C}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0147C24-4E3B-4AF6-B916-9F42E93A6E4C}"/>
   <bookViews>
-    <workbookView xWindow="-20010" yWindow="2415" windowWidth="13500" windowHeight="10545" activeTab="1" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="107">
   <si>
     <t>ID</t>
   </si>
@@ -331,6 +331,33 @@
   </si>
   <si>
     <t>Away_team_best_lineup</t>
+  </si>
+  <si>
+    <t>display_name</t>
+  </si>
+  <si>
+    <t>nicog01</t>
+  </si>
+  <si>
+    <t>officialmaje</t>
+  </si>
+  <si>
+    <t>glenm22</t>
+  </si>
+  <si>
+    <t>austinclifton</t>
+  </si>
+  <si>
+    <t>kingabes</t>
+  </si>
+  <si>
+    <t>bottomcap</t>
+  </si>
+  <si>
+    <t>treyclif3</t>
+  </si>
+  <si>
+    <t>nictrn</t>
   </si>
 </sst>
 </file>
@@ -702,13 +729,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE574477-F8B8-4C54-8D52-90DE47CC4CEE}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -719,10 +747,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -733,10 +764,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -747,10 +781,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -761,10 +798,13 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -775,10 +815,13 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -789,10 +832,13 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -803,10 +849,13 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -817,10 +866,13 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -831,6 +883,9 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" t="s">
         <v>74</v>
       </c>
     </row>
